--- a/Result/profitability/4702.xlsx
+++ b/Result/profitability/4702.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.21</v>
+        <v>0.24625</v>
       </c>
       <c r="N2" t="n">
-        <v>33.6925</v>
+        <v>36.20125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2175</v>
+        <v>0.21875</v>
       </c>
       <c r="N3" t="n">
-        <v>34.33</v>
+        <v>34.71375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>-0.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0.17375</v>
+        <v>0.23625</v>
       </c>
       <c r="N4" t="n">
-        <v>33.60375</v>
+        <v>32.28375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>-0.54</v>
       </c>
       <c r="M5" t="n">
-        <v>0.12875</v>
+        <v>0.2175</v>
       </c>
       <c r="N5" t="n">
-        <v>29.545</v>
+        <v>28.61875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>-0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1575</v>
+        <v>0.09625</v>
       </c>
       <c r="N6" t="n">
-        <v>26.92625</v>
+        <v>25.8075</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1268,10 +1268,10 @@
         <v>-0.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01625</v>
+        <v>-0.02499999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>23.775</v>
+        <v>23.69375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>-0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.07250000000000001</v>
+        <v>-0.08875</v>
       </c>
       <c r="N8" t="n">
-        <v>22.26375</v>
+        <v>21.94625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>12</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.73</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-91.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>37</v>
+      </c>
+      <c r="J75" t="n">
+        <v>26</v>
+      </c>
+      <c r="K75" t="n">
+        <v>23</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.60125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2888888888888889</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.540000000000006</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06815132814596203</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.82051282051282</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.410000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.175842429995254</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
